--- a/www/download/IND.compensation.emp.s.us.zdW16.xlsx
+++ b/www/download/IND.compensation.emp.s.us.zdW16.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>228286.287730193</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>214270.60066356</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>236988.459468206</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>302836.18414442</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.369</t>
+          <t>368526.444018213</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.407</t>
+          <t>407347.068764064</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.437</t>
+          <t>436920.442335109</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.531</t>
+          <t>530545.704777409</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.565</t>
+          <t>565215.179243737</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>545246.627971203</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0.688</t>
+          <t>687978.518613445</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>820086.46542994</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.848</t>
+          <t>848243.279663591</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>820453.507213221</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.784</t>
+          <t>783655.533317229</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>106568.163656</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>105581.549608</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>113776.180608</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>139381.079488</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>157560.683252</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>162871.239531</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>172554.446128</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>197800.194615</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>223306.798608</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>214718.873468</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>208067.063931</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>226659.12336</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>217595.629504</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>0.231</t>
+          <t>231135.046797</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>237169.82482</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>132203.08804</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>135708.20812</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>148437.16752</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>181166.31792</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>205284.29992</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>212888.27703</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>226094.38528</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>261023.37425</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>295682.86632</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.282</t>
+          <t>282246.42776</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>273400.70184</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>300115.2</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>285579.43392</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.302</t>
+          <t>302099.58675</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.305</t>
+          <t>304972.340221593</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6241.68181664874</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6778.39225495448</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7479.81623255256</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9610.98089565057</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11499.6596404714</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12765.8834595938</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14253.7419407361</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18229.4129710882</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23545.447614308</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23849.9414757046</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23659.0533875489</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26028.0190599412</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>25426.8281755285</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>28715.1500855694</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31252.7860700043</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.287</t>
+          <t>286764.527694148</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>246799.864308916</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>226901.661516056</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>236855.339605692</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.282</t>
+          <t>281625.76394464</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.376</t>
+          <t>376041.045922673</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.466</t>
+          <t>466335.084382145</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.585</t>
+          <t>585169.338135821</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.723</t>
+          <t>723188.424727551</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.752</t>
+          <t>751612.297771597</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1.007</t>
+          <t>1006835.71333107</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>1205162.08862886</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1.171</t>
+          <t>1171297.73597218</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>1.167</t>
+          <t>1166517.37287097</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>1.142</t>
+          <t>1142066.87338497</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.418</t>
+          <t>417515.336436275</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.421</t>
+          <t>420935.549132957</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.432</t>
+          <t>432069.481815337</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.508</t>
+          <t>508486.940052947</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.575</t>
+          <t>574654.688418547</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0.651</t>
+          <t>650866.49771912</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.733</t>
+          <t>733493.39671692</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.816</t>
+          <t>815539.915204537</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.869</t>
+          <t>869085.676439444</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.784</t>
+          <t>784222.62727675</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>0.888</t>
+          <t>888235.481075485</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>0.968</t>
+          <t>967793.433541088</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1.005</t>
+          <t>1005279.89653504</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>1.016</t>
+          <t>1016367.1689928</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0.975</t>
+          <t>974592.942193483</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.589</t>
+          <t>588648.261440248</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.649</t>
+          <t>648537.417706858</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.709</t>
+          <t>708806.495508411</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.787</t>
+          <t>787189.110926371</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0.924</t>
+          <t>923516.897971014</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1059897.96776983</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1.251</t>
+          <t>1251019.71548612</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>1588322.7047816</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2.158</t>
+          <t>2157847.77625412</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2.479</t>
+          <t>2478568.3015114</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>3.036</t>
+          <t>3036441.33114355</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>3.897</t>
+          <t>3896981.0192003</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>4.577</t>
+          <t>4577126.62759297</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>5.159</t>
+          <t>5158719.31798628</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>5.666</t>
+          <t>5665835.26711</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4991.96707756152</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5134.56383525791</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5790.87773499578</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7607.16169062565</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8977.88368506092</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9630.49494735292</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10275.5101594481</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11764.4272802749</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13198.5071455725</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12699.9225987404</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13275.5502349952</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14304.2066275393</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12872.0079293832</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12095.8211885877</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11488.1237643192</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27505.070351272</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>29963.52993018</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>37860.689840919</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>46713.171137596</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>55337.56730814</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>62839.47973198</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>71532.985157512</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>86554.098159179</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>109750.381303548</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>95479.045397567</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>97034.5751564</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>107288.836546311</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>98898.347084978</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>98911.850635509</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>95366.102107545</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.134</t>
+          <t>1134332.2704</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.118</t>
+          <t>1117823.4368</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1189784.1792</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1.429</t>
+          <t>1429100.3888</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1579817.6828</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1.584</t>
+          <t>1583912.2299</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>1.628</t>
+          <t>1627708.3604</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>1.825</t>
+          <t>1825074.2925</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2.027</t>
+          <t>2026672.6812</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1.929</t>
+          <t>1928817.3124</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1.887</t>
+          <t>1886562.5733</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>2.068</t>
+          <t>2067731.088</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1980457.5296</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>2.098</t>
+          <t>2097501.5325</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2.174</t>
+          <t>2173765.66058179</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>88180.226868</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>89605.32042</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>98345.433757</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>120821.122686</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>136345.742988</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>142950.806927</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>152593.537425</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>177175.836456</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>199645.365255</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>188274.106875</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>181025.240375</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>192282.708206817</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>180109.044566</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>188102.03365</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>0.193</t>
+          <t>193361.283482557</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>336799.88364</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.351</t>
+          <t>351185.09012</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.394</t>
+          <t>394371.27408</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.502</t>
+          <t>502174.86032</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.586</t>
+          <t>586390.00875</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0.631</t>
+          <t>630805.35375</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0.686</t>
+          <t>685992.28872</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0.809</t>
+          <t>809004.09425</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0.929</t>
+          <t>929065.23672</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>0.863</t>
+          <t>863020.08628</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>0.808</t>
+          <t>808465.81599</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>0.833</t>
+          <t>832683.4032</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>0.726</t>
+          <t>725883.7344</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>0.734</t>
+          <t>734126.93088</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>0.739</t>
+          <t>739383.916686971</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2666.53582850719</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2885.51724349765</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3371.34435374679</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4543.08067349507</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5536.80460510587</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6358.19558984601</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7693.70831560295</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10503.35092247</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12586.2966991226</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10359.8935331306</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9601.65464919127</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10825.3631923332</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10568.5041700282</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11814.9357443486</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12820.9068496977</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>65601.9226</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>66958.36972</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>72750.6816</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>89063.22208</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>101970.81713</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>107187.79929</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>114067.36764</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>131277.59105</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>150171.03328</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>141714.88804</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>136917.36801</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>150847.4208</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>144301.92656</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>150139.71285</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>151070.3775</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.752</t>
+          <t>751937.76444</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.761</t>
+          <t>760865.4882</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.837</t>
+          <t>836796.14352</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.031</t>
+          <t>1031001.132</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1.174</t>
+          <t>1173619.15244</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1.218</t>
+          <t>1218458.35254</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>1.284</t>
+          <t>1283976.18332</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>1.458</t>
+          <t>1457851.8326</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>1.614</t>
+          <t>1613747.19908</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.536</t>
+          <t>1536154.05328</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1.504</t>
+          <t>1504369.22895</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1.629</t>
+          <t>1629203.4816</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1.543</t>
+          <t>1542504.5416</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>1.621</t>
+          <t>1621123.21854</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1648332.55918132</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.915</t>
+          <t>914961.77223</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.929</t>
+          <t>929214.82776</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.005</t>
+          <t>1005347.28294</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.157</t>
+          <t>1157488.61829</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1.373</t>
+          <t>1372776.5652</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1.428</t>
+          <t>1428196.6404</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1.545</t>
+          <t>1544886.78882</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>1.789</t>
+          <t>1789003.50168</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>1.679</t>
+          <t>1678670.35172</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1.425</t>
+          <t>1424806.35456</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1.461</t>
+          <t>1460973.45285</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1.545</t>
+          <t>1544799.1952</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1.574</t>
+          <t>1573778.45506</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>1.594</t>
+          <t>1593656.75232</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>1.729</t>
+          <t>1729253.94108</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>56253.3941405882</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>58357.7454758137</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>70766.9956743822</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>93810.7576750172</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>110841.79911918</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>122614.015466927</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>129791.602927531</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>150794.333058145</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>168684.707020718</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>160977.742863799</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>147841.741793404</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>139076.45011518</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>115005.038162502</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>106044.348720476</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>103337.270128376</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23323.49442822</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26563.201154658</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32899.2686231328</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>42159.1833246455</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>50944.4144677055</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>55710.836036881</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>55921.1215869662</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>67895.288784639</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>77030.9644760446</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>63007.0092146915</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>60690.4730205928</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>65146.131968567</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>59194.6354353728</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>61494.0029505594</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>62694.0329448552</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>90303.9866791231</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>84414.1067305556</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>103484.588721022</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>127918.836172003</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>137447.982919183</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>146397.051427448</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>184091.784663292</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>219820.902877605</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>256591.455704771</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>270168.420960388</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>353759.979576064</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.418</t>
+          <t>418100.537944051</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.429</t>
+          <t>428966.473399493</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>430197.169784549</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.422</t>
+          <t>421707.261913733</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>235794.555800446</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>239690.113256321</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.244</t>
+          <t>244297.879288728</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>0.282</t>
+          <t>282387.807893002</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0.334</t>
+          <t>333844.663389734</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>382854.727645563</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>0.423</t>
+          <t>422894.607307721</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>539973.567329159</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>0.621</t>
+          <t>621416.055405493</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>0.649</t>
+          <t>649042.794429539</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>809581.247022344</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>0.925</t>
+          <t>925467.025260991</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>0.913</t>
+          <t>912811.065013584</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>0.937</t>
+          <t>937250.705962325</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>990200.259261768</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>46254.6152544787</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>49924.600495315</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>56418.2248736946</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>73151.7273415185</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>87552.07745356</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>96880.4071191097</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>106849.930737734</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>129001.584877783</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>142177.466275306</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>123802.469803946</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>108305.262476958</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>112507.840575246</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>103032.765155381</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>107538.412342932</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>111211.18801935</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.569</t>
+          <t>568761.1924</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.579</t>
+          <t>579253.929</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.638</t>
+          <t>638134.94496</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0.797</t>
+          <t>796960.15056</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0.912</t>
+          <t>912350.894</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>0.943</t>
+          <t>943035.14019</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>0.991</t>
+          <t>990578.37348</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1119906.67895</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1239736.43752</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>1.166</t>
+          <t>1165698.93924</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1.126</t>
+          <t>1125835.21431</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1.199</t>
+          <t>1199468.7216</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1.092</t>
+          <t>1091793.23264</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>1.119</t>
+          <t>1119216.96324</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1130163.65244963</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2.816</t>
+          <t>2815746.98017517</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2.415</t>
+          <t>2415279.67896613</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2.283</t>
+          <t>2282877.34837872</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2.481</t>
+          <t>2480875.94726225</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2.629</t>
+          <t>2629016.94674353</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2.623</t>
+          <t>2622651.06991303</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2.562</t>
+          <t>2562197.19764021</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2.499</t>
+          <t>2498606.06263854</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2.825</t>
+          <t>2825108.00660218</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2.954</t>
+          <t>2954291.44972516</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>3.159</t>
+          <t>3158809.2828684</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>3.446</t>
+          <t>3446481.09334626</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>3.419</t>
+          <t>3418845.63587703</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2809894.0431069</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2.588</t>
+          <t>2588002.54392296</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.327</t>
+          <t>326946.51755515</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>316783.749722492</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.355</t>
+          <t>354580.227185362</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>399970.242963151</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0.441</t>
+          <t>440511.026762419</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>0.524</t>
+          <t>523759.478420637</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>0.592</t>
+          <t>592150.758224056</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>649922.72188089</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>0.597</t>
+          <t>597086.470471031</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>0.529</t>
+          <t>528639.662754186</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>0.624</t>
+          <t>623546.383751446</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>0.681</t>
+          <t>680937.56094195</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>0.702</t>
+          <t>701801.659077351</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>0.756</t>
+          <t>756050.251712294</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>0.822</t>
+          <t>821661.974383707</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5127.06246830205</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5422.95637429398</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6318.64607780542</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8452.11931484176</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10504.6119598992</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12191.4529147747</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14764.5704486455</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19428.325410536</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23404.029213334</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18477.3558919898</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16674.522472558</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18859.2807471078</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18363.0392845664</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20178.0086426628</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>21331.270938851</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10208.9992739055</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10947.1306257508</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12401.4048085141</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>15287.7454972193</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17857.8729085335</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19085.0392471106</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20878.9548187799</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>24844.0556418033</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>28753.0785338397</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>28028.1978106935</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27692.0707537294</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>30546.0282507805</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29326.5081458503</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>32364.8782574298</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>34599.2278903424</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3660.86046100367</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3721.90352958466</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4023.41127999094</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4966.50457499411</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6173.60352950848</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7586.10005956143</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9898.27308660839</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>15089.9061746681</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18485.206695062</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13198.3879217523</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11185.2095491152</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12374.6873478486</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12370.6944229751</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13707.9732139619</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14713.5898656293</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>222557.701398238</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>242996.711723845</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>260890.203512604</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>250819.971520876</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>259967.593334322</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>288973.009038836</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>316045.854718983</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>337437.169451314</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.361</t>
+          <t>360831.526858095</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>298767.012882749</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>336592.718104172</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>366982.102186924</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>370346.042745876</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>398158.603851226</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.405</t>
+          <t>404887.611140761</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2006.90042983854</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2051.16313074228</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2235.11320414116</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2730.39966196382</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3061.05654089106</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3461.54580393645</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3628.74126338817</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4187.65925957624</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5236.77792014259</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4355.41272667832</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4368.69562097534</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4963.58131937692</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4745.59666240938</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5122.78567635186</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5519.3494688472</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>234886.2576</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>239968.8552</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>265358.0544</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.326</t>
+          <t>325656.6432</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0.363</t>
+          <t>363074.5076</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>370021.4661</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>387566.052</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>0.449</t>
+          <t>449384.209</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>0.509</t>
+          <t>509374.81</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>0.489</t>
+          <t>489392.0812</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>0.463</t>
+          <t>463243.3281</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>0.499</t>
+          <t>498962.4</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>0.467</t>
+          <t>466925.8704</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>0.485</t>
+          <t>485112.4308</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>0.492</t>
+          <t>492493.549</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>85304.272748817</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>97785.4416775753</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>96177.8400751323</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>102118.522606331</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>112403.224672269</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>132996.417001372</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>148756.228458876</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>185640.448560253</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>244635.665261069</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>196420.520884067</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>212825.414697109</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>232229.961189892</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>217991.268495875</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>231768.044826209</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>241318.349447873</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>66573.742782602</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>68274.6563741539</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>74853.6401083371</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>91779.3008224205</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>103325.112915802</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>107866.063845997</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>111386.143639843</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>126438.328653965</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>139891.449500806</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>132083.530151212</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>126748.879554182</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>128332.394980546</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>109819.83543509</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>114198.453209169</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>114218.832658478</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16853.6987306169</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19176.0605332431</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20560.3177218463</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>25168.2823046459</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>31729.0055545692</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>43991.8918801262</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>53111.9352728305</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>69054.2055802199</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>90113.6364353751</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>70023.0410691147</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>70251.8877853129</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>73536.0799716865</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>65472.0671868118</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>70967.1518031497</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>76752.4538062128</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>114157.265587553</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>140292.566269018</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>167393.480441693</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>212108.033004503</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>291357.79391856</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>0.358</t>
+          <t>357623.831331478</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>464258.700883244</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>0.634</t>
+          <t>634045.000969024</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>0.838</t>
+          <t>838027.66291</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>0.663</t>
+          <t>663285.324091058</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>0.783</t>
+          <t>783264.866852056</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>0.948</t>
+          <t>948193.750885118</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1.048</t>
+          <t>1047901.78999335</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>1.108</t>
+          <t>1107508.43141786</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>1.027</t>
+          <t>1026786.50477773</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9261.9552159524</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9350.782877922</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10907.7460093141</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14588.3490031015</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17986.6750950025</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20641.4352968497</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23834.9656753049</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>31921.6429686861</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>40521.8704183616</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>40019.4933228012</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>39594.7034793902</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>43233.9699830967</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>40875.669714652</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>42994.9050382179</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>44342.5362429497</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11892.6881167295</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12187.7699604307</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13703.0084144848</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17015.5229765542</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19732.1613792298</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20753.0127773947</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>22273.6204687774</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26672.3958402405</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31473.735150386</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>29649.2101884721</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>28564.9214031948</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30044.3488326818</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>27091.3360373735</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27589.3601502296</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>28102.5630742369</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>125191.300661877</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>118015.305087275</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>129288.803330567</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>160836.374917403</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>183303.796960623</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>186294.566558412</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>197667.731787319</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>232389.625702087</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>251281.270708597</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>215864.512905543</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>235609.917431781</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>274735.143898353</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>272865.473194269</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>291883.189070697</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>288875.852157231</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>110517.227671272</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>80011.2426880812</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>81916.1168548035</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>104194.11031238</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>132875.966183165</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>166834.054112298</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>176569.718392115</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>216989.67000379</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>246902.969237804</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>209210.39196354</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>248306.483912359</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>263069.481937508</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>0.269</t>
+          <t>268810.687767447</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>0.277</t>
+          <t>277019.472668986</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>0.269</t>
+          <t>269473.128882797</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.513</t>
+          <t>512506.974176429</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.491</t>
+          <t>490727.451099204</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.523</t>
+          <t>523342.817449876</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0.513</t>
+          <t>513397.343549848</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0.534</t>
+          <t>534008.453688601</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0.575</t>
+          <t>575227.885146496</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>0.587</t>
+          <t>587147.94261415</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>0.584</t>
+          <t>584469.817944494</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>0.593</t>
+          <t>592988.352785281</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>0.566</t>
+          <t>565572.91012444</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>0.624</t>
+          <t>624266.422881021</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>0.668</t>
+          <t>668477.954374237</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>0.685</t>
+          <t>684812.939121424</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>699785.808310394</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>0.704</t>
+          <t>704467.922649437</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6.215</t>
+          <t>6215147.80314446</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>6.423</t>
+          <t>6423146.43420744</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>6519691.34384195</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>6.772</t>
+          <t>6772090.25714787</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>7.167</t>
+          <t>7166902.59873644</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>7.539</t>
+          <t>7539079.37444122</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>7.986</t>
+          <t>7985511.94723064</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>8.369</t>
+          <t>8369068.73031058</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>8.54</t>
+          <t>8540298.39291486</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8250330.92288482</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>8.417</t>
+          <t>8417431.13619961</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>8.74</t>
+          <t>8740156.61422045</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>9120483.96233394</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>9.349</t>
+          <t>9349299.15897539</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>9.771</t>
+          <t>9771294.96707294</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1.801</t>
+          <t>1800814.50077968</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1.789</t>
+          <t>1789202.57038073</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>1.729</t>
+          <t>1728612.29782657</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1.921</t>
+          <t>1921291.95444887</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2.243</t>
+          <t>2242788.54385591</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2.632</t>
+          <t>2632073.64092198</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>3.068</t>
+          <t>3067601.81602745</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>3.612</t>
+          <t>3611752.4499459</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>4.328</t>
+          <t>4328141.77644798</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>4090391.87821205</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>4.726</t>
+          <t>4725835.92444684</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>5.445</t>
+          <t>5445439.58486657</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>5.882</t>
+          <t>5882302.32646808</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>6.059</t>
+          <t>6059367.5567379</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>6.161</t>
+          <t>6160678.94237295</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19070413.6996621</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>18.929</t>
+          <t>18928549.6680496</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>19.525</t>
+          <t>19524790.2509453</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>21.751</t>
+          <t>21751377.0438138</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>24.133</t>
+          <t>24133290.910503</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>25.863</t>
+          <t>25862970.8257554</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>27.869</t>
+          <t>27868718.708084</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>31.105</t>
+          <t>31104617.4993084</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>34.391</t>
+          <t>34391272.0989663</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>33.077</t>
+          <t>33077161.0130693</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>35.582</t>
+          <t>35581769.4747042</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>39.468</t>
+          <t>39467876.5738791</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>40.562</t>
+          <t>40561562.0428979</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>41.498</t>
+          <t>41497945.4177504</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>42.541</t>
+          <t>42541022.6510366</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4337,84 +4342,84 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14058.2773338164</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14227.5935239663</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16837.9436053174</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21722.6100515903</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25598.350673904</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27722.0047107369</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30330.7892984034</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>36306.3519428676</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>42887.1134134228</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>39528.1836597952</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>35505.8379457055</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>36441.0535508881</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32770.4694782475</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32562.3595582048</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>31714.0152300433</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4424,84 +4429,84 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>175068.339479657</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>177542.289264167</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>192018.658221289</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>225708.653287684</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>242664.270561385</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>248315.58159179</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>255019.836659806</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>278431.373819329</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>0.332</t>
+          <t>331616.056997717</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>0.335</t>
+          <t>334724.071850213</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>0.361</t>
+          <t>360523.762265751</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>439751.54938027</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>0.419</t>
+          <t>419022.034017657</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>429750.632077853</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>0.443</t>
+          <t>442941.399661282</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4511,84 +4516,84 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>78028.3749192772</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>80985.9328967418</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>95922.756360814</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>110170.981708347</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>122025.243507881</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>135312.393482932</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>148591.566544745</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>180305.322098969</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>0.207</t>
+          <t>207195.93247822</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>190419.32413751</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>202069.863592381</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>231570.19161041</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>0.238</t>
+          <t>237890.404897611</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>249440.376640236</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>243143.963322222</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4600,7 +4605,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4612,7 +4617,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4624,7 +4629,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4636,7 +4641,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4648,7 +4653,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4695,6 +4700,11 @@
           <t>compensation.emp.s.us</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4729,6 +4739,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW16</t>
